--- a/reports/20260507/API_role_validity_claude.xlsx
+++ b/reports/20260507/API_role_validity_claude.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>roleId=377, userId=453, email=roleval_f5c4f8_9f2e9a38@test.hirepro.in, initial validity_till=None (expected null)</t>
+          <t>roleId=397, userId=479, email=roleval_f37a73_5176c90f@test.hirepro.in, initial validity_till=None (expected null)</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>message='Updated successfully.', expected~=2026-06-06 11:46:31, stored=2026-06-06 11:46:32</t>
+          <t>message='Updated successfully.', expected~=2026-06-06 18:38:57, stored=2026-06-06 18:39:01</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>userId=453, roleId=377, validityTill=2026-06-06T11:46:32</t>
+          <t>userId=479, roleId=397, validityTill=2026-06-06T18:39:01</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>email=roleval_f5c4f8_60bc84d8@test.hirepro.in, message='Updated successfully.', expected~=2026-06-06 11:46:34, stored=2026-06-06 11:46:35</t>
+          <t>email=roleval_f37a73_043b5a1a@test.hirepro.in, message='Updated successfully.', expected~=2026-06-06 18:39:10, stored=2026-06-06 18:39:11</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>old=2026-06-06T11:46:32, new=2026-05-17 11:46:41, expected~=2026-05-17 11:46:36</t>
+          <t>old=2026-06-06T18:39:01, new=2026-05-17 18:39:21, expected~=2026-05-17 18:39:13</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>userId=453, roleId=383, validity_till=None (expected null)</t>
+          <t>userId=479, roleId=407, validity_till=None (expected null)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>filter=IsUserRoleValidityOver=false, role=377, user=453, total=1, found_in_page=False</t>
+          <t>filter=IsUserRoleValidityOver=false, role=397, user=479, total=1, found_in_page=False</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>userA: msg='Updated successfully.', stored=2026-07-06 11:46:50, expected~=2026-07-06 11:46:49 | userB: msg='Updated successfully.', stored=2026-08-05 11:46:50, expected~=2026-08-05 11:46:49</t>
+          <t>userA: msg='Updated successfully.', stored=2026-07-06 18:39:36, expected~=2026-07-06 18:39:35 | userB: msg='Updated successfully.', stored=2026-08-05 18:39:36, expected~=2026-08-05 18:39:35</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>message='Updated successfully.', expected~=2027-05-07 11:46:52, stored=2027-05-07 11:46:53</t>
+          <t>message='Updated successfully.', expected~=2027-05-07 18:39:38, stored=2027-05-07 18:39:38</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>message='Updated successfully.', expected~=2026-05-08 11:46:58, stored=2026-05-08 11:46:59</t>
+          <t>message='Updated successfully.', expected~=2026-05-08 18:39:40, stored=2026-05-08 18:39:40</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403</t>
+          <t>HTTP 200, error='Users not found.'</t>
         </is>
       </c>
     </row>
